--- a/docs/07_Evaluacion/Lista_de_Chequeo_Final_del_Proyecto_ADSO_SENA.xlsx
+++ b/docs/07_Evaluacion/Lista_de_Chequeo_Final_del_Proyecto_ADSO_SENA.xlsx
@@ -801,7 +801,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Version 1.0  |  11 de septiembre de 2026  |  Elaboro: Harryson Andres [apellidos por completar]  |  Reviso: Jessica [apellidos por completar] Miguel Mendez  |  Instructor: Juan Carlos Quintero Romero</t>
+          <t>Version 1.1  |  13 de septiembre de 2026  |  Elaboro: Harryson [apellidos por completar]  |  Reviso: Jessica [apellidos por completar]  |  Instructor: Juan Carlos Quintero Romero</t>
         </is>
       </c>
     </row>
@@ -3297,13 +3297,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="46" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
@@ -4037,7 +4030,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Siete modulos funcionales, 108 pruebas, imagen de contenedor, cinco migraciones versionadas, base administrada con TLS.</t>
+          <t>Trece modulos funcionales, 61 endpoints con permiso verificado, doce entidades, tres migraciones versionadas, base administrada en Neon y empaquetado en contenedores escrito y validado.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4067,12 +4060,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Seguridad con denegacion por omision y aislamiento probado; 108 pruebas; integracion continua con ramas protegidas; MAN-01 y MAN-02; TRZ-01 con 53 de 57 requisitos en cobertura completa (93%).</t>
+          <t>Seguridad con los ocho hallazgos cerrados y propiedad del recurso comprobada en el servidor; 32 pruebas de unidad y 27 comprobaciones de integracion; integracion continua en cada envio; manuales tecnico y de usuario; matriz de trazabilidad de 85 filas sin huecos.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>La correspondencia entre la version entregada y la documentada, que depende de incorporar las tres ramas pendientes y etiquetar v1.0.0.</t>
+          <t>Falta ejecutar el empaquetado en contenedores y configurar el proveedor de correo, y falta la etiqueta de version que ligue lo entregado con lo documentado.</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4450,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Jessica [apellidos por completar] Miguel Mendez</t>
+          <t>Jessica [apellidos por completar]</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr"/>
